--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N6_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>17.3318318201375</v>
       </c>
       <c r="E2" t="n">
-        <v>21.39539137594888</v>
+        <v>17.52570047170689</v>
       </c>
       <c r="F2" t="n">
-        <v>1.028614763093833</v>
+        <v>3.376504416798716</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>19.38906134632517</v>
       </c>
       <c r="E3" t="n">
-        <v>21.39539137594888</v>
+        <v>17.52570047170689</v>
       </c>
       <c r="F3" t="n">
-        <v>1.028614763093833</v>
+        <v>3.376504416798716</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,6 +529,38 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0065F0001T0006Z000C1N6.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>43.87608489799009</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.42291284620261</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.52570047170689</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.376504416798716</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T2485</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>G3</t>
         </is>

--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.29028855461318</v>
+        <v>10.12217189012464</v>
       </c>
       <c r="D2" t="n">
-        <v>17.3318318201375</v>
+        <v>2.816422670772344</v>
       </c>
       <c r="E2" t="n">
-        <v>17.52570047170689</v>
+        <v>2.84792632665237</v>
       </c>
       <c r="F2" t="n">
-        <v>3.376504416798716</v>
+        <v>0.5486819677297913</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49950580271542</v>
+        <v>3.168669692941255</v>
       </c>
       <c r="D3" t="n">
-        <v>19.38906134632517</v>
+        <v>3.15072246877784</v>
       </c>
       <c r="E3" t="n">
-        <v>17.52570047170689</v>
+        <v>2.84792632665237</v>
       </c>
       <c r="F3" t="n">
-        <v>3.376504416798716</v>
+        <v>0.5486819677297913</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.87608489799009</v>
+        <v>7.12986379592339</v>
       </c>
       <c r="D4" t="n">
-        <v>11.42291284620261</v>
+        <v>1.856223337507923</v>
       </c>
       <c r="E4" t="n">
-        <v>17.52570047170689</v>
+        <v>2.84792632665237</v>
       </c>
       <c r="F4" t="n">
-        <v>3.376504416798716</v>
+        <v>0.5486819677297913</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
